--- a/artfynd/A 51906-2019 artfynd.xlsx
+++ b/artfynd/A 51906-2019 artfynd.xlsx
@@ -8004,7 +8004,7 @@
         <v>113334421</v>
       </c>
       <c r="B65" t="n">
-        <v>90635</v>
+        <v>90651</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>

--- a/artfynd/A 51906-2019 artfynd.xlsx
+++ b/artfynd/A 51906-2019 artfynd.xlsx
@@ -8004,7 +8004,7 @@
         <v>113334421</v>
       </c>
       <c r="B65" t="n">
-        <v>90651</v>
+        <v>90663</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>

--- a/artfynd/A 51906-2019 artfynd.xlsx
+++ b/artfynd/A 51906-2019 artfynd.xlsx
@@ -8004,7 +8004,7 @@
         <v>113334421</v>
       </c>
       <c r="B65" t="n">
-        <v>90663</v>
+        <v>90685</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>

--- a/artfynd/A 51906-2019 artfynd.xlsx
+++ b/artfynd/A 51906-2019 artfynd.xlsx
@@ -8004,7 +8004,7 @@
         <v>113334421</v>
       </c>
       <c r="B65" t="n">
-        <v>90685</v>
+        <v>90689</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>

--- a/artfynd/A 51906-2019 artfynd.xlsx
+++ b/artfynd/A 51906-2019 artfynd.xlsx
@@ -8004,7 +8004,7 @@
         <v>113334421</v>
       </c>
       <c r="B65" t="n">
-        <v>90689</v>
+        <v>90695</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>

--- a/artfynd/A 51906-2019 artfynd.xlsx
+++ b/artfynd/A 51906-2019 artfynd.xlsx
@@ -8004,7 +8004,7 @@
         <v>113334421</v>
       </c>
       <c r="B65" t="n">
-        <v>90695</v>
+        <v>90702</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>

--- a/artfynd/A 51906-2019 artfynd.xlsx
+++ b/artfynd/A 51906-2019 artfynd.xlsx
@@ -8004,7 +8004,7 @@
         <v>113334421</v>
       </c>
       <c r="B65" t="n">
-        <v>90702</v>
+        <v>90707</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>

--- a/artfynd/A 51906-2019 artfynd.xlsx
+++ b/artfynd/A 51906-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
